--- a/academias/Humanidades - Estadisticos 20231.xlsx
+++ b/academias/Humanidades - Estadisticos 20231.xlsx
@@ -803,19 +803,19 @@
         <v>26</v>
       </c>
       <c r="D9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9">
         <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>71.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>28.2</v>
+        <v>28.9</v>
       </c>
       <c r="I9" s="2">
         <v>5.8</v>
@@ -838,19 +838,19 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="I10" s="2">
         <v>6.5</v>
@@ -908,28 +908,28 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12">
         <v>9</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="H12" s="1">
-        <v>50</v>
+        <v>52.6</v>
       </c>
       <c r="I12" s="2">
         <v>5.6</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -940,28 +940,28 @@
         <v>18</v>
       </c>
       <c r="D13">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E13">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F13">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G13" s="1">
-        <v>71.8</v>
+        <v>71</v>
       </c>
       <c r="H13" s="1">
-        <v>28.2</v>
+        <v>29</v>
       </c>
       <c r="I13" s="2">
         <v>5.9</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1284,19 +1284,19 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23">
         <v>9</v>
       </c>
       <c r="G23" s="1">
-        <v>73.5</v>
+        <v>74.3</v>
       </c>
       <c r="H23" s="1">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="I23" s="2">
         <v>7.7</v>
@@ -1319,19 +1319,19 @@
         <v>38</v>
       </c>
       <c r="D24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F24">
         <v>7</v>
       </c>
       <c r="G24" s="1">
-        <v>82.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="H24" s="1">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="I24" s="2">
         <v>7.1</v>
@@ -1491,19 +1491,19 @@
         <v>18</v>
       </c>
       <c r="D29">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E29">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F29">
         <v>88</v>
       </c>
       <c r="G29" s="1">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H29" s="1">
-        <v>31.7</v>
+        <v>31.4</v>
       </c>
       <c r="I29" s="2">
         <v>7</v>
@@ -1520,28 +1520,28 @@
         <v>20</v>
       </c>
       <c r="D30">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E30">
         <v>552</v>
       </c>
       <c r="F30">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G30" s="1">
-        <v>76.3</v>
+        <v>76.2</v>
       </c>
       <c r="H30" s="1">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="I30" s="2">
         <v>7.2</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1845,13 +1845,13 @@
         <v>26</v>
       </c>
       <c r="D9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1880,13 +1880,13 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1950,13 +1950,13 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1982,13 +1982,13 @@
         <v>18</v>
       </c>
       <c r="D13">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -2326,13 +2326,13 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -2361,13 +2361,13 @@
         <v>38</v>
       </c>
       <c r="D24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -2533,13 +2533,13 @@
         <v>18</v>
       </c>
       <c r="D29">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -2551,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -2562,13 +2562,13 @@
         <v>20</v>
       </c>
       <c r="D30">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -2580,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="K30" s="1">
         <v>100</v>
@@ -2887,19 +2887,19 @@
         <v>26</v>
       </c>
       <c r="D9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9">
         <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>71.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>28.2</v>
+        <v>28.9</v>
       </c>
       <c r="I9" s="2">
         <v>6</v>
@@ -2922,19 +2922,19 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="I10" s="2">
         <v>6.5</v>
@@ -2992,28 +2992,28 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12">
         <v>9</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="H12" s="1">
-        <v>50</v>
+        <v>52.6</v>
       </c>
       <c r="I12" s="2">
         <v>5.7</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3024,28 +3024,28 @@
         <v>18</v>
       </c>
       <c r="D13">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E13">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F13">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G13" s="1">
-        <v>71.8</v>
+        <v>71</v>
       </c>
       <c r="H13" s="1">
-        <v>28.2</v>
+        <v>29</v>
       </c>
       <c r="I13" s="2">
         <v>6.1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3368,19 +3368,19 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23">
         <v>9</v>
       </c>
       <c r="G23" s="1">
-        <v>73.5</v>
+        <v>74.3</v>
       </c>
       <c r="H23" s="1">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="I23" s="2">
         <v>7.4</v>
@@ -3403,19 +3403,19 @@
         <v>38</v>
       </c>
       <c r="D24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F24">
         <v>7</v>
       </c>
       <c r="G24" s="1">
-        <v>82.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="H24" s="1">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="I24" s="2">
         <v>7.2</v>
@@ -3575,19 +3575,19 @@
         <v>18</v>
       </c>
       <c r="D29">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E29">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F29">
         <v>88</v>
       </c>
       <c r="G29" s="1">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H29" s="1">
-        <v>31.7</v>
+        <v>31.4</v>
       </c>
       <c r="I29" s="2">
         <v>7</v>
@@ -3604,28 +3604,28 @@
         <v>20</v>
       </c>
       <c r="D30">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E30">
         <v>552</v>
       </c>
       <c r="F30">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G30" s="1">
-        <v>76.3</v>
+        <v>76.2</v>
       </c>
       <c r="H30" s="1">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="I30" s="2">
         <v>7.3</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Humanidades - Estadisticos 20231.xlsx
+++ b/academias/Humanidades - Estadisticos 20231.xlsx
@@ -564,19 +564,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>78.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="H2" s="1">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="I2" s="2">
         <v>7.5</v>
@@ -596,19 +596,19 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>78.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="H3" s="1">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="I3" s="2">
         <v>7.5</v>
@@ -701,10 +701,10 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -733,10 +733,10 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -803,19 +803,19 @@
         <v>26</v>
       </c>
       <c r="D9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9">
         <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>71.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="H9" s="1">
-        <v>28.9</v>
+        <v>28.2</v>
       </c>
       <c r="I9" s="2">
         <v>5.8</v>
@@ -926,10 +926,10 @@
         <v>5.6</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -940,28 +940,28 @@
         <v>18</v>
       </c>
       <c r="D13">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E13">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F13">
         <v>49</v>
       </c>
       <c r="G13" s="1">
-        <v>71</v>
+        <v>71.2</v>
       </c>
       <c r="H13" s="1">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="I13" s="2">
         <v>5.9</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -978,16 +978,16 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>86.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="I14" s="2">
         <v>8.4</v>
@@ -1045,16 +1045,16 @@
         <v>66</v>
       </c>
       <c r="E16">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1">
-        <v>89.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>10.6</v>
+        <v>9.1</v>
       </c>
       <c r="I16" s="2">
         <v>8.6</v>
@@ -1284,19 +1284,19 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23">
         <v>9</v>
       </c>
       <c r="G23" s="1">
-        <v>74.3</v>
+        <v>73.5</v>
       </c>
       <c r="H23" s="1">
-        <v>25.7</v>
+        <v>26.5</v>
       </c>
       <c r="I23" s="2">
         <v>7.7</v>
@@ -1392,16 +1392,16 @@
         <v>30</v>
       </c>
       <c r="E26">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G26" s="1">
-        <v>43.3</v>
+        <v>46.7</v>
       </c>
       <c r="H26" s="1">
-        <v>56.7</v>
+        <v>53.3</v>
       </c>
       <c r="I26" s="2">
         <v>6.2</v>
@@ -1491,19 +1491,19 @@
         <v>18</v>
       </c>
       <c r="D29">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E29">
         <v>192</v>
       </c>
       <c r="F29">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G29" s="1">
-        <v>68.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="H29" s="1">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="I29" s="2">
         <v>7</v>
@@ -1523,25 +1523,25 @@
         <v>724</v>
       </c>
       <c r="E30">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F30">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G30" s="1">
-        <v>76.2</v>
+        <v>76.5</v>
       </c>
       <c r="H30" s="1">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="I30" s="2">
         <v>7.2</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1606,28 +1606,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1638,28 +1638,28 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1676,25 +1676,25 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>3.3</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1711,25 +1711,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>9.4</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1743,28 +1743,28 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1775,28 +1775,28 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F7">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1813,25 +1813,25 @@
         <v>36</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="J8">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1845,28 +1845,28 @@
         <v>26</v>
       </c>
       <c r="D9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>48.7</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>51.3</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J9">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1883,25 +1883,25 @@
         <v>39</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F10">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>43.6</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="J10">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1918,25 +1918,25 @@
         <v>37</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>48.6</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>51.4</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J11">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1953,25 +1953,25 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>57.9</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J12">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1982,28 +1982,28 @@
         <v>18</v>
       </c>
       <c r="D13">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="F13">
-        <v>169</v>
+        <v>88</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>48.2</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>51.8</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="J13">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2122,25 +2122,25 @@
         <v>24</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F17">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>79.2</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>20.8</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J17">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2157,25 +2157,25 @@
         <v>24</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J18">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2192,25 +2192,25 @@
         <v>25</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J19">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2224,25 +2224,25 @@
         <v>73</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F20">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>79.5</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>20.5</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J20">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2259,25 +2259,25 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F21">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J21">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2294,25 +2294,25 @@
         <v>24</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F22">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>45.8</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>54.2</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J22">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2326,28 +2326,28 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F23">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>23.5</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J23">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2364,25 +2364,25 @@
         <v>40</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F24">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2399,25 +2399,25 @@
         <v>39</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F25">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>79.5</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>20.5</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J25">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2434,25 +2434,25 @@
         <v>30</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F26">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>26.7</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J26">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2469,25 +2469,25 @@
         <v>42</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F27">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J27">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2504,25 +2504,25 @@
         <v>43</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F28">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>18.6</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J28">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2533,28 +2533,28 @@
         <v>18</v>
       </c>
       <c r="D29">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="F29">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>22.2</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J29">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2565,25 +2565,25 @@
         <v>724</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="F30">
-        <v>724</v>
+        <v>244</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>66.3</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>33.7</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J30">
-        <v>724</v>
+        <v>66</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -2648,22 +2648,22 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>78.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="H2" s="1">
-        <v>21.6</v>
+        <v>25</v>
       </c>
       <c r="I2" s="2">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2680,22 +2680,22 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>78.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="H3" s="1">
-        <v>21.6</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>3.3</v>
       </c>
       <c r="I4" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2785,10 +2785,10 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2800,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2817,10 +2817,10 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -2855,19 +2855,19 @@
         <v>36</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G8" s="1">
-        <v>69.40000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="H8" s="1">
-        <v>30.6</v>
+        <v>58.3</v>
       </c>
       <c r="I8" s="2">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2887,22 +2887,22 @@
         <v>26</v>
       </c>
       <c r="D9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1">
-        <v>71.09999999999999</v>
+        <v>48.7</v>
       </c>
       <c r="H9" s="1">
-        <v>28.9</v>
+        <v>51.3</v>
       </c>
       <c r="I9" s="2">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2925,19 +2925,19 @@
         <v>39</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1">
-        <v>82.09999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="H10" s="1">
-        <v>17.9</v>
+        <v>43.6</v>
       </c>
       <c r="I10" s="2">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2960,19 +2960,19 @@
         <v>37</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G11" s="1">
-        <v>73</v>
+        <v>48.6</v>
       </c>
       <c r="H11" s="1">
-        <v>27</v>
+        <v>51.4</v>
       </c>
       <c r="I11" s="2">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2995,25 +2995,25 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1">
-        <v>47.4</v>
+        <v>42.1</v>
       </c>
       <c r="H12" s="1">
-        <v>52.6</v>
+        <v>57.9</v>
       </c>
       <c r="I12" s="2">
         <v>5.7</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3024,28 +3024,28 @@
         <v>18</v>
       </c>
       <c r="D13">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E13">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="F13">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="G13" s="1">
-        <v>71</v>
+        <v>48.2</v>
       </c>
       <c r="H13" s="1">
-        <v>29</v>
+        <v>51.8</v>
       </c>
       <c r="I13" s="2">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3062,16 +3062,16 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>86.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="I14" s="2">
         <v>8.4</v>
@@ -3129,16 +3129,16 @@
         <v>66</v>
       </c>
       <c r="E16">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1">
-        <v>89.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>10.6</v>
+        <v>9.1</v>
       </c>
       <c r="I16" s="2">
         <v>8.6</v>
@@ -3164,19 +3164,19 @@
         <v>24</v>
       </c>
       <c r="E17">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>66.7</v>
+        <v>79.2</v>
       </c>
       <c r="H17" s="1">
-        <v>33.3</v>
+        <v>20.8</v>
       </c>
       <c r="I17" s="2">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3234,19 +3234,19 @@
         <v>25</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H19" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I19" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3266,19 +3266,19 @@
         <v>73</v>
       </c>
       <c r="E20">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F20">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G20" s="1">
-        <v>78.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="H20" s="1">
-        <v>21.9</v>
+        <v>20.5</v>
       </c>
       <c r="I20" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3301,19 +3301,19 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F21">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="H21" s="1">
-        <v>44.4</v>
+        <v>33.3</v>
       </c>
       <c r="I21" s="2">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3348,7 +3348,7 @@
         <v>54.2</v>
       </c>
       <c r="I22" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3368,22 +3368,22 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23">
         <v>26</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="1">
-        <v>74.3</v>
+        <v>76.5</v>
       </c>
       <c r="H23" s="1">
-        <v>25.7</v>
+        <v>23.5</v>
       </c>
       <c r="I23" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3406,19 +3406,19 @@
         <v>40</v>
       </c>
       <c r="E24">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G24" s="1">
-        <v>82.5</v>
+        <v>87.5</v>
       </c>
       <c r="H24" s="1">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="I24" s="2">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3441,19 +3441,19 @@
         <v>39</v>
       </c>
       <c r="E25">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F25">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G25" s="1">
-        <v>66.7</v>
+        <v>79.5</v>
       </c>
       <c r="H25" s="1">
-        <v>33.3</v>
+        <v>20.5</v>
       </c>
       <c r="I25" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>30</v>
       </c>
       <c r="E26">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F26">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G26" s="1">
-        <v>43.3</v>
+        <v>73.3</v>
       </c>
       <c r="H26" s="1">
-        <v>56.7</v>
+        <v>26.7</v>
       </c>
       <c r="I26" s="2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3511,19 +3511,19 @@
         <v>42</v>
       </c>
       <c r="E27">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="1">
-        <v>90.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="I27" s="2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3546,19 +3546,19 @@
         <v>43</v>
       </c>
       <c r="E28">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F28">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G28" s="1">
-        <v>69.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H28" s="1">
-        <v>30.2</v>
+        <v>18.6</v>
       </c>
       <c r="I28" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3575,22 +3575,22 @@
         <v>18</v>
       </c>
       <c r="D29">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E29">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="F29">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="G29" s="1">
-        <v>68.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="H29" s="1">
-        <v>31.4</v>
+        <v>22.2</v>
       </c>
       <c r="I29" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3607,25 +3607,25 @@
         <v>724</v>
       </c>
       <c r="E30">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="F30">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="G30" s="1">
-        <v>76.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>23.8</v>
+        <v>25.4</v>
       </c>
       <c r="I30" s="2">
         <v>7.3</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Humanidades - Estadisticos 20231.xlsx
+++ b/academias/Humanidades - Estadisticos 20231.xlsx
@@ -2020,25 +2020,25 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F14">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>13.9</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J14">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2055,25 +2055,25 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F15">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>6.7</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2087,25 +2087,25 @@
         <v>66</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F16">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>10.6</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J16">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2565,25 +2565,25 @@
         <v>724</v>
       </c>
       <c r="E30">
-        <v>480</v>
+        <v>539</v>
       </c>
       <c r="F30">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="G30" s="1">
-        <v>66.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H30" s="1">
-        <v>33.7</v>
+        <v>25.6</v>
       </c>
       <c r="I30" s="2">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3062,19 +3062,19 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>88.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="I14" s="2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>6.7</v>
       </c>
       <c r="I15" s="2">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3129,19 +3129,19 @@
         <v>66</v>
       </c>
       <c r="E16">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="1">
-        <v>90.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>9.1</v>
+        <v>10.6</v>
       </c>
       <c r="I16" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3607,19 +3607,19 @@
         <v>724</v>
       </c>
       <c r="E30">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F30">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G30" s="1">
-        <v>74.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H30" s="1">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="I30" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J30">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20231.xlsx
+++ b/academias/Humanidades - Estadisticos 20231.xlsx
@@ -1621,7 +1621,7 @@
         <v>25</v>
       </c>
       <c r="I2" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>25</v>
       </c>
       <c r="I3" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>25.6</v>
       </c>
       <c r="I30" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -2663,7 +2663,7 @@
         <v>25</v>
       </c>
       <c r="I2" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2695,7 +2695,7 @@
         <v>25</v>
       </c>
       <c r="I3" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3619,7 +3619,7 @@
         <v>25.6</v>
       </c>
       <c r="I30" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J30">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20231.xlsx
+++ b/academias/Humanidades - Estadisticos 20231.xlsx
@@ -1392,19 +1392,19 @@
         <v>30</v>
       </c>
       <c r="E26">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F26">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G26" s="1">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="H26" s="1">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="I26" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1494,19 +1494,19 @@
         <v>279</v>
       </c>
       <c r="E29">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F29">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G29" s="1">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="H29" s="1">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="I29" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1523,16 +1523,16 @@
         <v>724</v>
       </c>
       <c r="E30">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F30">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G30" s="1">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="H30" s="1">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="I30" s="2">
         <v>7.2</v>
@@ -2651,16 +2651,16 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>75</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>25</v>
+        <v>13.9</v>
       </c>
       <c r="I2" s="2">
         <v>7.1</v>
@@ -2683,16 +2683,16 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>75</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>25</v>
+        <v>13.9</v>
       </c>
       <c r="I3" s="2">
         <v>7.1</v>
@@ -2730,7 +2730,7 @@
         <v>3.3</v>
       </c>
       <c r="I4" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2753,16 +2753,16 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>90.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
       <c r="I5" s="2">
         <v>8.300000000000001</v>
@@ -2800,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2820,19 +2820,19 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H7" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2855,19 +2855,19 @@
         <v>36</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="H8" s="1">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="I8" s="2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2890,19 +2890,19 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G9" s="1">
-        <v>48.7</v>
+        <v>61.5</v>
       </c>
       <c r="H9" s="1">
-        <v>51.3</v>
+        <v>38.5</v>
       </c>
       <c r="I9" s="2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2925,19 +2925,19 @@
         <v>39</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G10" s="1">
-        <v>56.4</v>
+        <v>61.5</v>
       </c>
       <c r="H10" s="1">
-        <v>43.6</v>
+        <v>38.5</v>
       </c>
       <c r="I10" s="2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2960,19 +2960,19 @@
         <v>37</v>
       </c>
       <c r="E11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1">
-        <v>48.6</v>
+        <v>54.1</v>
       </c>
       <c r="H11" s="1">
-        <v>51.4</v>
+        <v>45.9</v>
       </c>
       <c r="I11" s="2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2995,19 +2995,19 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>42.1</v>
+        <v>73.7</v>
       </c>
       <c r="H12" s="1">
-        <v>57.9</v>
+        <v>26.3</v>
       </c>
       <c r="I12" s="2">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3027,19 +3027,19 @@
         <v>170</v>
       </c>
       <c r="E13">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="G13" s="1">
-        <v>48.2</v>
+        <v>58.8</v>
       </c>
       <c r="H13" s="1">
-        <v>51.8</v>
+        <v>41.2</v>
       </c>
       <c r="I13" s="2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3062,19 +3062,19 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>86.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="H14" s="1">
-        <v>13.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I14" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3097,19 +3097,19 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3129,19 +3129,19 @@
         <v>66</v>
       </c>
       <c r="E16">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>89.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="H16" s="1">
-        <v>10.6</v>
+        <v>4.5</v>
       </c>
       <c r="I16" s="2">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3176,7 +3176,7 @@
         <v>20.8</v>
       </c>
       <c r="I17" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>25</v>
       </c>
       <c r="I18" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3246,7 +3246,7 @@
         <v>16</v>
       </c>
       <c r="I19" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3278,7 +3278,7 @@
         <v>20.5</v>
       </c>
       <c r="I20" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3301,19 +3301,19 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G21" s="1">
-        <v>66.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>33.3</v>
+        <v>25.9</v>
       </c>
       <c r="I21" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3336,19 +3336,19 @@
         <v>24</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G22" s="1">
-        <v>45.8</v>
+        <v>66.7</v>
       </c>
       <c r="H22" s="1">
-        <v>54.2</v>
+        <v>33.3</v>
       </c>
       <c r="I22" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3371,16 +3371,16 @@
         <v>34</v>
       </c>
       <c r="E23">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G23" s="1">
-        <v>76.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H23" s="1">
-        <v>23.5</v>
+        <v>20.6</v>
       </c>
       <c r="I23" s="2">
         <v>7.6</v>
@@ -3406,16 +3406,16 @@
         <v>40</v>
       </c>
       <c r="E24">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G24" s="1">
-        <v>87.5</v>
+        <v>92.5</v>
       </c>
       <c r="H24" s="1">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="I24" s="2">
         <v>7.8</v>
@@ -3441,19 +3441,19 @@
         <v>39</v>
       </c>
       <c r="E25">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G25" s="1">
-        <v>79.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H25" s="1">
-        <v>20.5</v>
+        <v>17.9</v>
       </c>
       <c r="I25" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>30</v>
       </c>
       <c r="E26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G26" s="1">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="H26" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="I26" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3511,19 +3511,19 @@
         <v>42</v>
       </c>
       <c r="E27">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>92.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H27" s="1">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3546,19 +3546,19 @@
         <v>43</v>
       </c>
       <c r="E28">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" s="1">
-        <v>81.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>18.6</v>
+        <v>20.9</v>
       </c>
       <c r="I28" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3578,16 +3578,16 @@
         <v>279</v>
       </c>
       <c r="E29">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F29">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G29" s="1">
-        <v>77.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H29" s="1">
-        <v>22.2</v>
+        <v>17.9</v>
       </c>
       <c r="I29" s="2">
         <v>7.4</v>
@@ -3607,16 +3607,16 @@
         <v>724</v>
       </c>
       <c r="E30">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="F30">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="G30" s="1">
-        <v>74.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="H30" s="1">
-        <v>25.6</v>
+        <v>20</v>
       </c>
       <c r="I30" s="2">
         <v>7.3</v>

--- a/academias/Humanidades - Estadisticos 20231.xlsx
+++ b/academias/Humanidades - Estadisticos 20231.xlsx
@@ -2651,16 +2651,16 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>86.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="I2" s="2">
         <v>7.1</v>
@@ -2683,16 +2683,16 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>86.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="I3" s="2">
         <v>7.1</v>
@@ -3607,16 +3607,16 @@
         <v>724</v>
       </c>
       <c r="E30">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F30">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G30" s="1">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="I30" s="2">
         <v>7.3</v>

--- a/academias/Humanidades - Estadisticos 20231.xlsx
+++ b/academias/Humanidades - Estadisticos 20231.xlsx
@@ -2663,7 +2663,7 @@
         <v>11.1</v>
       </c>
       <c r="I2" s="2">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2695,7 +2695,7 @@
         <v>11.1</v>
       </c>
       <c r="I3" s="2">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>3.3</v>
       </c>
       <c r="I4" s="2">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2765,7 +2765,7 @@
         <v>3.1</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2800,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2832,7 +2832,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="2">
-        <v>8.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2867,7 +2867,7 @@
         <v>50</v>
       </c>
       <c r="I8" s="2">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2902,7 +2902,7 @@
         <v>38.5</v>
       </c>
       <c r="I9" s="2">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2937,7 +2937,7 @@
         <v>38.5</v>
       </c>
       <c r="I10" s="2">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>45.9</v>
       </c>
       <c r="I11" s="2">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3007,7 +3007,7 @@
         <v>26.3</v>
       </c>
       <c r="I12" s="2">
-        <v>6.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>41.2</v>
       </c>
       <c r="I13" s="2">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3074,7 +3074,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I14" s="2">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3141,7 +3141,7 @@
         <v>4.5</v>
       </c>
       <c r="I16" s="2">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3176,7 +3176,7 @@
         <v>20.8</v>
       </c>
       <c r="I17" s="2">
-        <v>6.9</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>25</v>
       </c>
       <c r="I18" s="2">
-        <v>6.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3246,7 +3246,7 @@
         <v>16</v>
       </c>
       <c r="I19" s="2">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3278,7 +3278,7 @@
         <v>20.5</v>
       </c>
       <c r="I20" s="2">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3313,7 +3313,7 @@
         <v>25.9</v>
       </c>
       <c r="I21" s="2">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3348,7 +3348,7 @@
         <v>33.3</v>
       </c>
       <c r="I22" s="2">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>20.6</v>
       </c>
       <c r="I23" s="2">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3418,7 +3418,7 @@
         <v>7.5</v>
       </c>
       <c r="I24" s="2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3453,7 +3453,7 @@
         <v>17.9</v>
       </c>
       <c r="I25" s="2">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3488,7 +3488,7 @@
         <v>30</v>
       </c>
       <c r="I26" s="2">
-        <v>6.6</v>
+        <v>8.5</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3558,7 +3558,7 @@
         <v>20.9</v>
       </c>
       <c r="I28" s="2">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3590,7 +3590,7 @@
         <v>17.9</v>
       </c>
       <c r="I29" s="2">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3619,7 +3619,7 @@
         <v>19.9</v>
       </c>
       <c r="I30" s="2">
-        <v>7.3</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20231.xlsx
+++ b/academias/Humanidades - Estadisticos 20231.xlsx
@@ -2663,7 +2663,7 @@
         <v>11.1</v>
       </c>
       <c r="I2" s="2">
-        <v>9.4</v>
+        <v>7.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2695,7 +2695,7 @@
         <v>11.1</v>
       </c>
       <c r="I3" s="2">
-        <v>9.4</v>
+        <v>7.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>3.3</v>
       </c>
       <c r="I4" s="2">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2765,7 +2765,7 @@
         <v>3.1</v>
       </c>
       <c r="I5" s="2">
-        <v>9.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2800,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2832,7 +2832,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="2">
-        <v>9.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2855,19 +2855,19 @@
         <v>36</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
-        <v>50</v>
+        <v>52.8</v>
       </c>
       <c r="H8" s="1">
-        <v>50</v>
+        <v>47.2</v>
       </c>
       <c r="I8" s="2">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2902,7 +2902,7 @@
         <v>38.5</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>5.8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2925,19 +2925,19 @@
         <v>39</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G10" s="1">
-        <v>61.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>38.5</v>
+        <v>35.9</v>
       </c>
       <c r="I10" s="2">
-        <v>8.1</v>
+        <v>6.2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>45.9</v>
       </c>
       <c r="I11" s="2">
-        <v>7.7</v>
+        <v>5.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3007,7 +3007,7 @@
         <v>26.3</v>
       </c>
       <c r="I12" s="2">
-        <v>8.699999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3027,19 +3027,19 @@
         <v>170</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F13">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G13" s="1">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="H13" s="1">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="I13" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3074,7 +3074,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I14" s="2">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3141,7 +3141,7 @@
         <v>4.5</v>
       </c>
       <c r="I16" s="2">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3176,7 +3176,7 @@
         <v>20.8</v>
       </c>
       <c r="I17" s="2">
-        <v>9</v>
+        <v>6.9</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>25</v>
       </c>
       <c r="I18" s="2">
-        <v>8.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3246,7 +3246,7 @@
         <v>16</v>
       </c>
       <c r="I19" s="2">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3278,7 +3278,7 @@
         <v>20.5</v>
       </c>
       <c r="I20" s="2">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3313,7 +3313,7 @@
         <v>25.9</v>
       </c>
       <c r="I21" s="2">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3348,7 +3348,7 @@
         <v>33.3</v>
       </c>
       <c r="I22" s="2">
-        <v>8.300000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>20.6</v>
       </c>
       <c r="I23" s="2">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3418,7 +3418,7 @@
         <v>7.5</v>
       </c>
       <c r="I24" s="2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3453,7 +3453,7 @@
         <v>17.9</v>
       </c>
       <c r="I25" s="2">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3488,7 +3488,7 @@
         <v>30</v>
       </c>
       <c r="I26" s="2">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3558,7 +3558,7 @@
         <v>20.9</v>
       </c>
       <c r="I28" s="2">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3590,7 +3590,7 @@
         <v>17.9</v>
       </c>
       <c r="I29" s="2">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3607,19 +3607,19 @@
         <v>724</v>
       </c>
       <c r="E30">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F30">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G30" s="1">
-        <v>80.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H30" s="1">
-        <v>19.9</v>
+        <v>19.6</v>
       </c>
       <c r="I30" s="2">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="J30">
         <v>0</v>
